--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -3007,7 +3007,7 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>60歳以上の方の就業相談・職業紹介・技能講習を行う市の就業支援機関。</v>
+        <v>55歳以上の方の就業相談・職業紹介・技能講習を行う市の就業支援機関。</v>
       </c>
       <c r="H56" t="str">
         <v>【本人が60歳以上】</v>
@@ -3031,7 +3031,7 @@
         <v>名古屋市高齢者就業支援センター: https://www.bes-c.com/</v>
       </c>
       <c r="O56" t="str">
-        <v>parseInt(s.age) &gt;= 60</v>
+        <v>parseInt(s.age) &gt;= 55</v>
       </c>
     </row>
     <row r="57">
@@ -7038,7 +7038,7 @@
         <v>152</v>
       </c>
       <c r="B142" t="str">
-        <v>高齢者肺炎球菌(定期予防接種)</v>
+        <v>高齢者肺炎球菌予防接種(定期予防接種)</v>
       </c>
       <c r="C142" t="str">
         <v>医療・健康</v>
